--- a/Assets/@Resources/Data/Excel/BuffData.xlsx
+++ b/Assets/@Resources/Data/Excel/BuffData.xlsx
@@ -419,51 +419,71 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>BuffData</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>IconLabel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Timed</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DataId</t>
+          <t>int</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IconLabel</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Timed</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>버프ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>아이콘 주소</t>
+          <t>아이콘</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>지속시간형(TRUE/FALSE)</t>
+          <t>시간제여부</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>지속시간(초)</t>
+          <t>지속(초)</t>
         </is>
       </c>
     </row>
@@ -511,8 +531,10 @@
           <t>SpeedPotionBuffIcon</t>
         </is>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>15</v>
